--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19586,7 +19604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19662,6 +19680,91 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0016</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0016 'KVAL skupina A' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0017</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0017 'KVAL skupina B' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0018</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0018 'KVAL skupina C' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0095</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0095 'KVAL 1.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0096</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0096 'KVAL 2.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -23734,8 +23837,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -24035,7 +24136,6 @@
         </is>
       </c>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
@@ -50088,6 +50188,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0016</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1985_86_0016 'KVAL skupina A' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0017</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1985_86_0017 'KVAL skupina B' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0018</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1985_86_0018 'KVAL skupina C' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0095</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1985_86_0095 'KVAL 1.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0096</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1985_86_0096 'KVAL 2.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19604,7 +19604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19684,14 +19684,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1985_86_0016</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0016 'KVAL skupina A' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19701,14 +19696,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1985_86_0017</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0017 'KVAL skupina B' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19718,14 +19708,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1985_86_0018</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0018 'KVAL skupina C' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19735,14 +19720,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1985_86_0095</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0095 'KVAL 1.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19752,17 +19732,600 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1985_86_0096</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1985_86_0096 'KVAL 2.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23837,6 +24400,8 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -23867,6 +24432,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0001</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -24099,6 +24669,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0003</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -24111,6 +24686,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0003</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -24123,6 +24703,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0026</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -24136,6 +24721,7 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
@@ -26855,12 +27441,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27285,12 +27871,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -27369,12 +27955,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -27453,12 +28039,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -27626,12 +28212,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -27836,12 +28422,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -28814,12 +29400,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -28940,12 +29526,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29862,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -29365,12 +29951,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -29538,12 +30124,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -29993,12 +30579,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -30040,12 +30626,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -31118,12 +31704,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -32822,12 +33408,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -32995,12 +33581,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -33314,12 +33900,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33591,12 +34177,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -34051,12 +34637,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -36329,12 +36915,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -37573,12 +38159,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Třebenice</t>
+          <t>MDPM Lovosice</t>
         </is>
       </c>
     </row>
@@ -37615,12 +38201,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -37699,12 +38285,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -37835,12 +38421,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -37877,12 +38463,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -37917,19 +38503,14 @@
           <t>Divize I</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -38132,19 +38713,14 @@
           <t>Divize II</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -38181,12 +38757,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou.</t>
+          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou. || TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>ČSAD Hrádek nad Nisou</t>
+          <t>Hrádek nad Nisou</t>
         </is>
       </c>
     </row>
@@ -38263,19 +38839,14 @@
           <t>Divize II</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -38352,19 +38923,14 @@
           <t>Divize II</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -38441,19 +39007,14 @@
           <t>Divize II</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -38730,12 +39291,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -39412,12 +39973,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -40572,12 +41133,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Železný Brod = TJ ŽB Železný Brod (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Jablonec nL Nisou). **Železný Brod** = sklarsky mesto (vyrobce sklenenych ozdob - bizuteria, perlicky). 'ŽB' = zkratka Železný Brod. city Železný Brod.</t>
+          <t>Železný Brod = TJ ŽB Železný Brod (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Jablonec nL Nisou). **Železný Brod** = sklarsky mesto (vyrobce sklenenych ozdob - bizuteria, perlicky). 'ŽB' = zkratka Železný Brod. city Železný Brod. || TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>ŽB Železný Brod</t>
+          <t>Železný Brod</t>
         </is>
       </c>
     </row>
@@ -42553,12 +43114,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -42679,12 +43240,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -43057,12 +43618,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -43398,12 +43959,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -44474,12 +45035,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška.</t>
+          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška. || TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>RICO Veverská Bítýška</t>
+          <t>Veverská Bítýška</t>
         </is>
       </c>
     </row>
@@ -45124,12 +45685,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -45250,12 +45811,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -45757,12 +46318,12 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -47613,12 +48174,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -50194,11 +50755,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -50243,21 +50804,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1985_86_0016</t>
+          <t>CLUB_S1985_86_0009</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1985_86_0016 'KVAL skupina A' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -50265,21 +50824,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1985_86_0017</t>
+          <t>CLUB_S1985_86_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1985_86_0017 'KVAL skupina B' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -50287,21 +50844,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1985_86_0018</t>
+          <t>CLUB_S1985_86_0021</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1985_86_0018 'KVAL skupina C' (L25, parent=NODE_S1985_86_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -50309,21 +50864,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1985_86_0095</t>
+          <t>CLUB_S1985_86_0023</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1985_86_0095 'KVAL 1.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -50331,24 +50884,1002 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1985_86_0096</t>
+          <t>CLUB_S1985_86_0027</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1985_86_0096 'KVAL 2.kolo' (L25, parent=NODE_S1985_86_0019) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0032</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0064</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0067</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0075</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0077</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0081</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0091</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0092</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0117</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0155</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0159</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0159</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0166</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0172</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0182</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0231</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0260</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0261</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0263</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0266</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0267</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0268</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0268</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0273</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0273</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0274</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0276</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0276</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0278</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0278</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0280</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0280</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0286</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0300</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0303</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0320</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0328</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0372</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0375</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0378</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0384</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0391</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0392</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0398</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0416</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0431</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0434</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0445</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLUB_S1985_86_0490</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -71502,11 +73033,7 @@
           <t>CLUB_S1985_86_0268</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
+      <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
@@ -71731,11 +73258,7 @@
           <t>CLUB_S1985_86_0273</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
+      <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
@@ -71870,11 +73393,7 @@
           <t>CLUB_S1985_86_0276</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
@@ -71964,11 +73483,7 @@
           <t>CLUB_S1985_86_0278</t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
+      <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="n"/>
@@ -72058,11 +73573,7 @@
           <t>CLUB_S1985_86_0280</t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1984_85_0264</t>
-        </is>
-      </c>
+      <c r="R27" s="3" t="n"/>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19604,7 +19604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19686,7 +19686,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19698,7 +19698,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19710,7 +19710,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19722,7 +19722,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19734,7 +19734,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19746,7 +19746,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19758,7 +19758,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19770,7 +19770,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19782,7 +19782,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19794,7 +19794,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19806,7 +19806,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19818,7 +19818,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19830,7 +19830,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19842,7 +19842,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19854,7 +19854,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19866,7 +19866,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19878,7 +19878,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19890,7 +19890,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19902,7 +19902,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19914,7 +19914,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19938,7 +19938,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19950,7 +19950,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19962,7 +19962,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19986,7 +19986,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20046,7 +20046,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20058,7 +20058,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20070,7 +20070,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20094,7 +20094,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20106,7 +20106,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20118,7 +20118,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20130,7 +20130,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20142,7 +20142,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20154,7 +20154,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20178,7 +20178,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20190,7 +20190,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20202,7 +20202,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20214,118 +20214,10 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20342,7 +20234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20401,6 +20293,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20443,6 +20340,11 @@
           <t>12 týmů: základ + playoff (QF/SF/finále/o místo) + o udržení. Mistr: VSŽ Košice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20579,6 +20481,11 @@
           <t>ASD Dukla Jihlava "B" hrála svá domácí utkání v Písku.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20663,6 +20570,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21261,6 +21173,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0014</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21387,6 +21304,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0017</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21429,6 +21351,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0018</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21513,6 +21440,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0020</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -21555,6 +21487,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21597,6 +21534,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0022</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21639,6 +21581,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0023</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -21681,6 +21628,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0024</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -22064,6 +22016,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22106,6 +22063,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0026</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22573,6 +22535,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0040</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -22615,6 +22582,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0041</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -22746,6 +22718,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0043</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22788,6 +22765,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0044</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22830,6 +22812,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0045</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -23045,6 +23032,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0052</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -23087,6 +23079,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0053</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -23129,6 +23126,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0054</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23171,6 +23173,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0059</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -23213,6 +23220,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0060</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -23428,6 +23440,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0065</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23470,6 +23487,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0066</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23596,6 +23618,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0069</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23890,6 +23917,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0075</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23930,6 +23962,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1984_85_0076</t>
         </is>
       </c>
     </row>
@@ -27441,12 +27478,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -27955,12 +27992,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28039,12 +28076,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -28422,12 +28459,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -33581,12 +33618,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -33900,12 +33937,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38159,12 +38196,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>MDPM Lovosice</t>
+          <t>Třebenice</t>
         </is>
       </c>
     </row>
@@ -43240,12 +43277,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -45685,12 +45722,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -50755,7 +50792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50809,12 +50846,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0009</t>
+          <t>CLUB_S1985_86_0019</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50829,12 +50866,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0019</t>
+          <t>CLUB_S1985_86_0027</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50849,12 +50886,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0021</t>
+          <t>CLUB_S1985_86_0064</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50869,12 +50906,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0023</t>
+          <t>CLUB_S1985_86_0067</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50889,12 +50926,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0027</t>
+          <t>CLUB_S1985_86_0075</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50909,12 +50946,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0032</t>
+          <t>CLUB_S1985_86_0077</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50929,12 +50966,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0064</t>
+          <t>CLUB_S1985_86_0081</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50949,12 +50986,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0067</t>
+          <t>CLUB_S1985_86_0091</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50969,12 +51006,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0075</t>
+          <t>CLUB_S1985_86_0092</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50989,12 +51026,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0077</t>
+          <t>CLUB_S1985_86_0117</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51009,12 +51046,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0081</t>
+          <t>CLUB_S1985_86_0155</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51029,12 +51066,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0091</t>
+          <t>CLUB_S1985_86_0159</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51049,12 +51086,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0092</t>
+          <t>CLUB_S1985_86_0172</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51069,12 +51106,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0117</t>
+          <t>CLUB_S1985_86_0182</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51089,12 +51126,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0155</t>
+          <t>CLUB_S1985_86_0231</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51109,12 +51146,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0159</t>
+          <t>CLUB_S1985_86_0261</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51129,12 +51166,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0159</t>
+          <t>CLUB_S1985_86_0263</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51149,12 +51186,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0166</t>
+          <t>CLUB_S1985_86_0266</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51169,12 +51206,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0172</t>
+          <t>CLUB_S1985_86_0267</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51189,12 +51226,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0182</t>
+          <t>CLUB_S1985_86_0268</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51209,12 +51246,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0231</t>
+          <t>CLUB_S1985_86_0268</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51229,12 +51266,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0260</t>
+          <t>CLUB_S1985_86_0273</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51249,12 +51286,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0261</t>
+          <t>CLUB_S1985_86_0273</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51269,12 +51306,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0263</t>
+          <t>CLUB_S1985_86_0274</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51289,7 +51326,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0266</t>
+          <t>CLUB_S1985_86_0276</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -51309,12 +51346,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0267</t>
+          <t>CLUB_S1985_86_0276</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51329,7 +51366,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0268</t>
+          <t>CLUB_S1985_86_0278</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -51349,7 +51386,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0268</t>
+          <t>CLUB_S1985_86_0278</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -51369,7 +51406,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0273</t>
+          <t>CLUB_S1985_86_0280</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -51389,7 +51426,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0273</t>
+          <t>CLUB_S1985_86_0280</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -51409,12 +51446,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0274</t>
+          <t>CLUB_S1985_86_0286</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51429,12 +51466,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0276</t>
+          <t>CLUB_S1985_86_0300</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -51449,12 +51486,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0276</t>
+          <t>CLUB_S1985_86_0303</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51469,12 +51506,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0278</t>
+          <t>CLUB_S1985_86_0320</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51489,12 +51526,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0278</t>
+          <t>CLUB_S1985_86_0328</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51509,12 +51546,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0280</t>
+          <t>CLUB_S1985_86_0372</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51529,12 +51566,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0280</t>
+          <t>CLUB_S1985_86_0378</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -51549,12 +51586,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0286</t>
+          <t>CLUB_S1985_86_0384</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51569,12 +51606,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0300</t>
+          <t>CLUB_S1985_86_0391</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51589,12 +51626,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0303</t>
+          <t>CLUB_S1985_86_0392</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51609,12 +51646,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0320</t>
+          <t>CLUB_S1985_86_0398</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -51629,12 +51666,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0328</t>
+          <t>CLUB_S1985_86_0416</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ŽB Železný Brod' → 'Železný Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51649,12 +51686,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0372</t>
+          <t>CLUB_S1985_86_0434</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51669,12 +51706,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0375</t>
+          <t>CLUB_S1985_86_0445</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51689,197 +51726,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1985_86_0378</t>
+          <t>CLUB_S1985_86_0490</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0384</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0391</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0392</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0398</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0416</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0431</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0434</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0445</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0490</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -55656,7 +55656,7 @@
         <v>3</v>
       </c>
       <c r="J54" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -20234,7 +20234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20298,6 +20298,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24437,8 +24447,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -24758,7 +24766,6 @@
         </is>
       </c>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -20570,6 +20570,16 @@
           <t>NODE_S1985_86_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20584,6 +20594,14 @@
         <is>
           <t>NODE_S1984_85_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -20659,6 +20677,12 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20668,6 +20692,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -20701,6 +20733,16 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20710,6 +20752,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -20743,6 +20793,8 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20752,6 +20804,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -20785,6 +20845,8 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20794,6 +20856,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -20827,6 +20897,8 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20836,6 +20908,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -20869,6 +20949,8 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20878,6 +20960,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -20911,6 +21001,8 @@
           <t>NODE_S1985_86_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20920,6 +21012,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -21304,6 +21404,8 @@
           <t>NODE_S1985_86_0020</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21318,6 +21420,14 @@
         <is>
           <t>NODE_S1984_85_0017</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -21398,6 +21508,8 @@
           <t>NODE_S1985_86_0020</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21407,6 +21519,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -21628,6 +21748,8 @@
           <t>NODE_S1985_86_0026</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21642,6 +21764,14 @@
         <is>
           <t>NODE_S1984_85_0024</t>
         </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -21801,6 +21931,8 @@
           <t>NODE_S1985_86_0032</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21810,6 +21942,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -21843,6 +21983,8 @@
           <t>NODE_S1985_86_0032</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21852,6 +21994,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -21885,6 +22035,8 @@
           <t>NODE_S1985_86_0033</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21894,6 +22046,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -21927,6 +22087,8 @@
           <t>NODE_S1985_86_0033</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21936,6 +22098,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -21969,6 +22139,8 @@
           <t>NODE_S1985_86_0031</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21983,6 +22155,14 @@
         <is>
           <t>Finálová série II. SNHL. Ve finále je první utkání hráno doma.</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -22011,6 +22191,12 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0044</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22030,6 +22216,14 @@
         <is>
           <t>NODE_S1984_85_0025</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -22236,6 +22430,8 @@
           <t>NODE_S1985_86_0039</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22245,6 +22441,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -22409,6 +22613,8 @@
           <t>NODE_S1985_86_0039</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22418,6 +22624,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -22629,6 +22843,12 @@
           <t>NODE_S1985_86_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22638,6 +22858,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -22671,6 +22899,8 @@
           <t>NODE_S1985_86_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22680,6 +22910,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -23351,6 +23589,8 @@
           <t>NODE_S1985_86_0066</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23360,6 +23600,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -23534,6 +23782,8 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23543,6 +23793,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -23576,6 +23834,8 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23585,6 +23845,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -23665,6 +23933,8 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23674,6 +23944,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -23707,6 +23985,8 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23716,6 +23996,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -24011,6 +24299,16 @@
           <t>NODE_S1985_86_0082</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0085</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0086</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24020,6 +24318,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -24053,6 +24359,8 @@
           <t>NODE_S1985_86_0082</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24062,6 +24370,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -24095,6 +24411,8 @@
           <t>NODE_S1985_86_0082</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24104,6 +24422,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -24447,6 +24773,8 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -24650,6 +24978,8 @@
           <t>NODE_S1985_86_0093</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24659,6 +24989,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -24766,6 +25104,7 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>VSŽ Košice</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
@@ -20682,7 +20687,6 @@
           <t>NODE_S1985_86_0009</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20793,8 +20797,6 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20845,8 +20847,6 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20897,8 +20897,6 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20949,8 +20947,6 @@
           <t>NODE_S1985_86_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21001,8 +20997,6 @@
           <t>NODE_S1985_86_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21404,8 +21398,6 @@
           <t>NODE_S1985_86_0020</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21508,8 +21500,6 @@
           <t>NODE_S1985_86_0020</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21748,8 +21738,6 @@
           <t>NODE_S1985_86_0026</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21931,8 +21919,6 @@
           <t>NODE_S1985_86_0032</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21983,8 +21969,6 @@
           <t>NODE_S1985_86_0032</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22035,8 +22019,6 @@
           <t>NODE_S1985_86_0033</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22087,8 +22069,6 @@
           <t>NODE_S1985_86_0033</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22139,8 +22119,6 @@
           <t>NODE_S1985_86_0031</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22196,7 +22174,6 @@
           <t>NODE_S1985_86_0044</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22430,8 +22407,6 @@
           <t>NODE_S1985_86_0039</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22613,8 +22588,6 @@
           <t>NODE_S1985_86_0039</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22848,7 +22821,6 @@
           <t>NODE_S1985_86_0054</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22899,8 +22871,6 @@
           <t>NODE_S1985_86_0051</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23589,8 +23559,6 @@
           <t>NODE_S1985_86_0066</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23782,8 +23750,6 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23834,8 +23800,6 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23933,8 +23897,6 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23985,8 +23947,6 @@
           <t>NODE_S1985_86_0071</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24359,8 +24319,6 @@
           <t>NODE_S1985_86_0082</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24411,8 +24369,6 @@
           <t>NODE_S1985_86_0082</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24773,8 +24729,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -24978,8 +24932,6 @@
           <t>NODE_S1985_86_0093</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25104,7 +25056,6 @@
         </is>
       </c>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
@@ -50776,7 +50727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51124,6 +51075,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>1. kolo v Nitře, 2. kolo v Liptovském Mikuláši. Po rozšíření 2. SNHL postoupily i Kežmarok a Levoča.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VSŽ Košice</t>
         </is>
       </c>
     </row>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -57539,7 +57539,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>23</v>

--- a/data/S1985_86_FINAL.xlsx
+++ b/data/S1985_86_FINAL.xlsx
@@ -24729,6 +24729,8 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -25056,6 +25058,7 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
